--- a/AAII_Financials/Yearly/MMM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MMM_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>MMM</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>32681000</v>
+      </c>
+      <c r="E8" s="3">
         <v>34229000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35355000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>32184000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32136000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>32765000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>31657000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>30109000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30274000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>31821000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>30871000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>29904000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29611000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>18376000</v>
+      </c>
+      <c r="E9" s="3">
         <v>19229000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>18776000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16541000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17064000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16657000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15976000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15115000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15341000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16437000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16087000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15685000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15693000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>14305000</v>
+      </c>
+      <c r="E10" s="3">
         <v>15000000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>16579000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>15643000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15072000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>16108000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15681000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>14994000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14933000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15384000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14784000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14219000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13918000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1810000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1854000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1977000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1863000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1874000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1816000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1862000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1764000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1751000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1770000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1715000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1634000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1570000</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,38 +960,41 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>14901000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2394000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>135000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-184000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>168000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-410000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-583000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-111000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>114000</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
@@ -986,9 +1005,12 @@
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>41809000</v>
+      </c>
+      <c r="E17" s="3">
         <v>27690000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27997000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25033000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25998000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25558000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23869000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23082000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23328000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24686000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24205000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23421000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23433000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9128000</v>
+      </c>
+      <c r="E18" s="3">
         <v>6539000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7358000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7151000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6138000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7207000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7788000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7027000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6946000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7135000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6666000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6483000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6178000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>382000</v>
+      </c>
+      <c r="E20" s="3">
         <v>315000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>323000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>163000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-47000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>143000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>596000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>424000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>39000</v>
       </c>
       <c r="O20" s="3">
         <v>39000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>39000</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6759000</v>
+      </c>
+      <c r="E21" s="3">
         <v>8685000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>9596000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9225000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7684000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8838000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9928000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8925000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8377000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8536000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8035000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7810000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7453000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>942000</v>
+      </c>
+      <c r="E22" s="3">
         <v>462000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>477000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>519000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>448000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>350000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>836000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>398000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>119000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>102000</v>
       </c>
       <c r="M22" s="3">
         <v>102000</v>
       </c>
       <c r="N22" s="3">
+        <v>102000</v>
+      </c>
+      <c r="O22" s="3">
         <v>171000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>186000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9688000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6392000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7204000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6795000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5643000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7000000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7548000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7053000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6823000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7026000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6562000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6351000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6031000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2691000</v>
+      </c>
+      <c r="E24" s="3">
         <v>612000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1285000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1337000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1114000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1461000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1917000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1995000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1982000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2028000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1841000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1840000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1674000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6997000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5780000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5919000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5458000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4529000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5539000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5631000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5058000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4841000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4998000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4721000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4511000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4357000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6995000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5777000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5921000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5449000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4517000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5525000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5620000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5050000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4833000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4956000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4659000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4444000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4283000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1538,17 +1598,17 @@
       <c r="F29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-176000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-762000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-382000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-315000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-323000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-163000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>47000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-143000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-596000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-424000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-39000</v>
       </c>
       <c r="O32" s="3">
         <v>-39000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6995000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5777000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5921000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5449000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4517000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5349000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4858000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5050000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4833000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4956000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4659000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4444000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4283000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6995000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5777000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5921000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5449000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4517000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5349000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4858000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5050000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4833000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4956000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4659000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4444000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4283000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5933000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3655000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4564000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4634000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2353000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2853000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3053000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2398000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1798000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1897000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2581000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2883000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2219000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E42" s="3">
         <v>238000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>201000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>404000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>568000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>380000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1076000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>280000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>118000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1439000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>756000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1648000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1461000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4864000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4532000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4660000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4705000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4963000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5123000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4982000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4501000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4260000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4315000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4352000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4186000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3976000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4822000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5372000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4985000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4239000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4134000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4366000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4034000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3385000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3518000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3706000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3864000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3837000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3416000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>707000</v>
+      </c>
+      <c r="E45" s="3">
         <v>891000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>993000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1000000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>953000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>987000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1132000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1162000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1292000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1390000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1180000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1076000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1168000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16379000</v>
+      </c>
+      <c r="E46" s="3">
         <v>14688000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15403000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14982000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12971000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13709000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14277000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11726000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10986000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12303000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12733000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13630000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12240000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>967000</v>
+        <v>277000</v>
       </c>
       <c r="E47" s="3">
-        <v>262000</v>
+        <v>1040000</v>
       </c>
       <c r="F47" s="3">
-        <v>214000</v>
+        <v>313000</v>
       </c>
       <c r="G47" s="3">
-        <v>196000</v>
+        <v>263000</v>
       </c>
       <c r="H47" s="3">
-        <v>188000</v>
+        <v>263000</v>
       </c>
       <c r="I47" s="3">
-        <v>150000</v>
+        <v>256000</v>
       </c>
       <c r="J47" s="3">
         <v>213000</v>
       </c>
       <c r="K47" s="3">
+        <v>213000</v>
+      </c>
+      <c r="L47" s="3">
         <v>175000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>206000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1671000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1464000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1051000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9918000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10007000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10287000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10285000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10191000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8738000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8866000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8516000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8515000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8489000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8652000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8378000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7666000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17153000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17489000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18774000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19637000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19823000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12708000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13449000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11486000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11850000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8485000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9033000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9310000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8963000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3304000</v>
+        <v>6853000</v>
       </c>
       <c r="E52" s="3">
-        <v>2346000</v>
+        <v>3231000</v>
       </c>
       <c r="F52" s="3">
-        <v>2226000</v>
+        <v>2295000</v>
       </c>
       <c r="G52" s="3">
-        <v>1478000</v>
+        <v>2177000</v>
       </c>
       <c r="H52" s="3">
-        <v>1157000</v>
+        <v>1411000</v>
       </c>
       <c r="I52" s="3">
-        <v>1245000</v>
+        <v>1089000</v>
       </c>
       <c r="J52" s="3">
+        <v>1182000</v>
+      </c>
+      <c r="K52" s="3">
         <v>965000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1357000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1726000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1461000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1094000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1696000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>50580000</v>
+      </c>
+      <c r="E54" s="3">
         <v>46455000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>47072000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>47344000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>44659000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36500000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37987000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32906000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32883000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>31209000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33550000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33876000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31616000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3245000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3183000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2994000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2561000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2228000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2266000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1945000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1798000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1694000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1807000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1799000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1762000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1643000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2947000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1949000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1314000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>828000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2816000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1211000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1853000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>972000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2044000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>106000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1683000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1085000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>682000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9105000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4391000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4727000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4559000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4178000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3767000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3889000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3449000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3380000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4085000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4016000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3353000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3116000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15297000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9523000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9035000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7948000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9222000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7244000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7687000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6219000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7118000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5964000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7498000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6200000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5441000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13148000</v>
+      </c>
+      <c r="E61" s="3">
         <v>14076000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16149000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18082000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17629000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13486000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12156000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10723000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8799000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6764000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4384000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4987000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4484000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17267000</v>
+      </c>
+      <c r="E62" s="3">
         <v>8086000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6771000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8383000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7682000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5922000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6522000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5621000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5498000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5339000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3720000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4649000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5829000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45773000</v>
+      </c>
+      <c r="E66" s="3">
         <v>31733000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32026000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>34477000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34596000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26704000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26424000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>22608000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>21454000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18100000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16048000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16301000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16196000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>37479000</v>
+      </c>
+      <c r="E72" s="3">
         <v>47950000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>45821000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>43761000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>42135000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>40636000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>39115000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>37907000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>36296000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>34317000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>32416000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>30679000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>28348000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4807000</v>
+      </c>
+      <c r="E76" s="3">
         <v>14722000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15046000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12867000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10063000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9796000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11563000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10298000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11429000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13109000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17502000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17575000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15420000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6995000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5777000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5921000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5449000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4517000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5349000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4858000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5050000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4833000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4956000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4659000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4444000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4283000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1987000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1831000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1915000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1911000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1593000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1488000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1544000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1474000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1435000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1408000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1371000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1288000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1236000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6680000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5591000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7454000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8113000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7070000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6439000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6240000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6662000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6420000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6626000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5817000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5300000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5284000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1615000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1749000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1603000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1501000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1699000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1577000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1373000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1420000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1461000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1493000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1665000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1484000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1379000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1207000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1046000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1317000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-580000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6444000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>222000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3086000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1403000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2817000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-596000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-856000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2686000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2718000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-3311000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3369000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-3420000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-3388000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-3316000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-3193000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-2803000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2678000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2561000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2216000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1730000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1635000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1555000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3147000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5350000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6145000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5300000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1124000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6701000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2655000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4626000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3648000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6603000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5246000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2058000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3675000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-104000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-62000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>48000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-160000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>156000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-33000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-54000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-111000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-17000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>108000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-49000</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2278000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-909000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-70000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2281000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-500000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>655000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>600000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-99000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-684000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-302000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>664000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1158000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MMM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MMM_YR_FIN.xlsx
@@ -774,22 +774,22 @@
         <v>18376000</v>
       </c>
       <c r="E9" s="3">
-        <v>19229000</v>
+        <v>19232000</v>
       </c>
       <c r="F9" s="3">
-        <v>18776000</v>
+        <v>18795000</v>
       </c>
       <c r="G9" s="3">
-        <v>16541000</v>
+        <v>16499000</v>
       </c>
       <c r="H9" s="3">
         <v>17064000</v>
       </c>
       <c r="I9" s="3">
-        <v>16657000</v>
+        <v>16655000</v>
       </c>
       <c r="J9" s="3">
-        <v>15976000</v>
+        <v>15969000</v>
       </c>
       <c r="K9" s="3">
         <v>15115000</v>
@@ -819,22 +819,22 @@
         <v>14305000</v>
       </c>
       <c r="E10" s="3">
-        <v>15000000</v>
+        <v>14997000</v>
       </c>
       <c r="F10" s="3">
-        <v>16579000</v>
+        <v>16560000</v>
       </c>
       <c r="G10" s="3">
-        <v>15643000</v>
+        <v>15685000</v>
       </c>
       <c r="H10" s="3">
         <v>15072000</v>
       </c>
       <c r="I10" s="3">
-        <v>16108000</v>
+        <v>16110000</v>
       </c>
       <c r="J10" s="3">
-        <v>15681000</v>
+        <v>15688000</v>
       </c>
       <c r="K10" s="3">
         <v>14994000</v>
@@ -883,13 +883,13 @@
         <v>1810000</v>
       </c>
       <c r="E12" s="3">
-        <v>1854000</v>
+        <v>1862000</v>
       </c>
       <c r="F12" s="3">
-        <v>1977000</v>
+        <v>1994000</v>
       </c>
       <c r="G12" s="3">
-        <v>1863000</v>
+        <v>1862000</v>
       </c>
       <c r="H12" s="3">
         <v>1874000</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>14901000</v>
+        <v>14883000</v>
       </c>
       <c r="E14" s="3">
-        <v>-2394000</v>
+        <v>-344000</v>
       </c>
       <c r="F14" s="3">
-        <v>135000</v>
+        <v>88000</v>
       </c>
       <c r="G14" s="3">
-        <v>-184000</v>
+        <v>-139000</v>
       </c>
       <c r="H14" s="3">
-        <v>168000</v>
+        <v>330000</v>
       </c>
       <c r="I14" s="3">
-        <v>-410000</v>
+        <v>487000</v>
       </c>
       <c r="J14" s="3">
-        <v>-583000</v>
+        <v>-487000</v>
       </c>
       <c r="K14" s="3">
         <v>-111000</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1987000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1831000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1915000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1911000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1593000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1488000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1337000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>41809000</v>
+        <v>26797000</v>
       </c>
       <c r="E17" s="3">
-        <v>27690000</v>
+        <v>27786000</v>
       </c>
       <c r="F17" s="3">
-        <v>27997000</v>
+        <v>27601000</v>
       </c>
       <c r="G17" s="3">
-        <v>25033000</v>
+        <v>25028000</v>
       </c>
       <c r="H17" s="3">
-        <v>25998000</v>
+        <v>25831000</v>
       </c>
       <c r="I17" s="3">
-        <v>25558000</v>
+        <v>24998000</v>
       </c>
       <c r="J17" s="3">
-        <v>23869000</v>
+        <v>24324000</v>
       </c>
       <c r="K17" s="3">
         <v>23082000</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-9128000</v>
+        <v>5884000</v>
       </c>
       <c r="E18" s="3">
-        <v>6539000</v>
+        <v>6443000</v>
       </c>
       <c r="F18" s="3">
-        <v>7358000</v>
+        <v>7754000</v>
       </c>
       <c r="G18" s="3">
-        <v>7151000</v>
+        <v>7156000</v>
       </c>
       <c r="H18" s="3">
-        <v>6138000</v>
+        <v>6305000</v>
       </c>
       <c r="I18" s="3">
-        <v>7207000</v>
+        <v>7767000</v>
       </c>
       <c r="J18" s="3">
-        <v>7788000</v>
+        <v>7333000</v>
       </c>
       <c r="K18" s="3">
         <v>7027000</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>382000</v>
+        <v>-18000</v>
       </c>
       <c r="E20" s="3">
-        <v>315000</v>
+        <v>-11000</v>
       </c>
       <c r="F20" s="3">
-        <v>323000</v>
+        <v>-10000</v>
       </c>
       <c r="G20" s="3">
-        <v>163000</v>
+        <v>5000</v>
       </c>
       <c r="H20" s="3">
-        <v>-47000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>143000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>596000</v>
+        <v>-36000</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K20" s="3">
         <v>424000</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-6759000</v>
+        <v>7889000</v>
       </c>
       <c r="E21" s="3">
-        <v>8685000</v>
+        <v>8285000</v>
       </c>
       <c r="F21" s="3">
-        <v>9596000</v>
+        <v>9679000</v>
       </c>
       <c r="G21" s="3">
-        <v>9225000</v>
+        <v>9062000</v>
       </c>
       <c r="H21" s="3">
-        <v>7684000</v>
+        <v>7934000</v>
       </c>
       <c r="I21" s="3">
-        <v>8838000</v>
+        <v>9255000</v>
       </c>
       <c r="J21" s="3">
-        <v>9928000</v>
+        <v>8670000</v>
       </c>
       <c r="K21" s="3">
         <v>8925000</v>
@@ -1281,10 +1281,10 @@
         <v>462000</v>
       </c>
       <c r="F22" s="3">
-        <v>477000</v>
+        <v>488000</v>
       </c>
       <c r="G22" s="3">
-        <v>519000</v>
+        <v>529000</v>
       </c>
       <c r="H22" s="3">
         <v>448000</v>
@@ -1293,7 +1293,7 @@
         <v>350000</v>
       </c>
       <c r="J22" s="3">
-        <v>836000</v>
+        <v>322000</v>
       </c>
       <c r="K22" s="3">
         <v>398000</v>
@@ -1320,16 +1320,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-9688000</v>
+        <v>-9670000</v>
       </c>
       <c r="E23" s="3">
-        <v>6392000</v>
+        <v>6403000</v>
       </c>
       <c r="F23" s="3">
-        <v>7204000</v>
+        <v>7214000</v>
       </c>
       <c r="G23" s="3">
-        <v>6795000</v>
+        <v>6790000</v>
       </c>
       <c r="H23" s="3">
         <v>5643000</v>
@@ -1380,10 +1380,10 @@
         <v>1114000</v>
       </c>
       <c r="I24" s="3">
-        <v>1461000</v>
+        <v>1637000</v>
       </c>
       <c r="J24" s="3">
-        <v>1917000</v>
+        <v>2679000</v>
       </c>
       <c r="K24" s="3">
         <v>1995000</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-6997000</v>
+        <v>-6979000</v>
       </c>
       <c r="E26" s="3">
-        <v>5780000</v>
+        <v>5791000</v>
       </c>
       <c r="F26" s="3">
-        <v>5919000</v>
+        <v>5929000</v>
       </c>
       <c r="G26" s="3">
-        <v>5458000</v>
+        <v>5453000</v>
       </c>
       <c r="H26" s="3">
         <v>4529000</v>
       </c>
       <c r="I26" s="3">
-        <v>5539000</v>
+        <v>5363000</v>
       </c>
       <c r="J26" s="3">
-        <v>5631000</v>
+        <v>4869000</v>
       </c>
       <c r="K26" s="3">
         <v>5058000</v>
@@ -1515,10 +1515,10 @@
         <v>4517000</v>
       </c>
       <c r="I27" s="3">
-        <v>5525000</v>
+        <v>5349000</v>
       </c>
       <c r="J27" s="3">
-        <v>5620000</v>
+        <v>4858000</v>
       </c>
       <c r="K27" s="3">
         <v>5050000</v>
@@ -1589,26 +1589,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-176000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-762000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-382000</v>
+        <v>18000</v>
       </c>
       <c r="E32" s="3">
-        <v>-315000</v>
+        <v>11000</v>
       </c>
       <c r="F32" s="3">
-        <v>-323000</v>
+        <v>10000</v>
       </c>
       <c r="G32" s="3">
-        <v>-163000</v>
+        <v>-5000</v>
       </c>
       <c r="H32" s="3">
-        <v>47000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-143000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-596000</v>
+        <v>36000</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K32" s="3">
         <v>-424000</v>
@@ -2047,10 +2047,10 @@
         <v>201000</v>
       </c>
       <c r="G42" s="3">
-        <v>404000</v>
+        <v>411000</v>
       </c>
       <c r="H42" s="3">
-        <v>568000</v>
+        <v>98000</v>
       </c>
       <c r="I42" s="3">
         <v>380000</v>
@@ -2086,13 +2086,13 @@
         <v>4864000</v>
       </c>
       <c r="E43" s="3">
-        <v>4532000</v>
+        <v>4635000</v>
       </c>
       <c r="F43" s="3">
-        <v>4660000</v>
+        <v>4770000</v>
       </c>
       <c r="G43" s="3">
-        <v>4705000</v>
+        <v>4830000</v>
       </c>
       <c r="H43" s="3">
         <v>4963000</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>707000</v>
+        <v>222000</v>
       </c>
       <c r="E45" s="3">
-        <v>891000</v>
+        <v>353000</v>
       </c>
       <c r="F45" s="3">
-        <v>993000</v>
+        <v>229000</v>
       </c>
       <c r="G45" s="3">
-        <v>1000000</v>
+        <v>193000</v>
       </c>
       <c r="H45" s="3">
-        <v>953000</v>
+        <v>719000</v>
       </c>
       <c r="I45" s="3">
-        <v>987000</v>
+        <v>246000</v>
       </c>
       <c r="J45" s="3">
-        <v>1132000</v>
+        <v>195000</v>
       </c>
       <c r="K45" s="3">
         <v>1162000</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>277000</v>
+        <v>244000</v>
       </c>
       <c r="E47" s="3">
-        <v>1040000</v>
+        <v>967000</v>
       </c>
       <c r="F47" s="3">
-        <v>313000</v>
+        <v>262000</v>
       </c>
       <c r="G47" s="3">
-        <v>263000</v>
+        <v>214000</v>
       </c>
       <c r="H47" s="3">
-        <v>263000</v>
+        <v>213000</v>
       </c>
       <c r="I47" s="3">
-        <v>256000</v>
+        <v>207000</v>
       </c>
       <c r="J47" s="3">
-        <v>213000</v>
+        <v>171000</v>
       </c>
       <c r="K47" s="3">
         <v>213000</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6853000</v>
+        <v>1968000</v>
       </c>
       <c r="E52" s="3">
-        <v>3231000</v>
+        <v>2345000</v>
       </c>
       <c r="F52" s="3">
-        <v>2295000</v>
+        <v>1765000</v>
       </c>
       <c r="G52" s="3">
-        <v>2177000</v>
+        <v>1355000</v>
       </c>
       <c r="H52" s="3">
-        <v>1411000</v>
+        <v>940000</v>
       </c>
       <c r="I52" s="3">
-        <v>1089000</v>
+        <v>773000</v>
       </c>
       <c r="J52" s="3">
-        <v>1182000</v>
+        <v>713000</v>
       </c>
       <c r="K52" s="3">
         <v>965000</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2947000</v>
+        <v>3172000</v>
       </c>
       <c r="E58" s="3">
-        <v>1949000</v>
+        <v>2199000</v>
       </c>
       <c r="F58" s="3">
-        <v>1314000</v>
+        <v>1577000</v>
       </c>
       <c r="G58" s="3">
-        <v>828000</v>
+        <v>1084000</v>
       </c>
       <c r="H58" s="3">
-        <v>2816000</v>
+        <v>3063000</v>
       </c>
       <c r="I58" s="3">
-        <v>1211000</v>
+        <v>1242000</v>
       </c>
       <c r="J58" s="3">
-        <v>1853000</v>
+        <v>1854000</v>
       </c>
       <c r="K58" s="3">
         <v>972000</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9105000</v>
+        <v>6619000</v>
       </c>
       <c r="E59" s="3">
-        <v>4391000</v>
+        <v>2150000</v>
       </c>
       <c r="F59" s="3">
-        <v>4727000</v>
+        <v>2090000</v>
       </c>
       <c r="G59" s="3">
-        <v>4559000</v>
+        <v>2346000</v>
       </c>
       <c r="H59" s="3">
-        <v>4178000</v>
+        <v>2092000</v>
       </c>
       <c r="I59" s="3">
-        <v>3767000</v>
+        <v>1852000</v>
       </c>
       <c r="J59" s="3">
-        <v>3889000</v>
+        <v>1948000</v>
       </c>
       <c r="K59" s="3">
         <v>3449000</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>13148000</v>
+        <v>13770000</v>
       </c>
       <c r="E61" s="3">
-        <v>14076000</v>
+        <v>14758000</v>
       </c>
       <c r="F61" s="3">
-        <v>16149000</v>
+        <v>16740000</v>
       </c>
       <c r="G61" s="3">
-        <v>18082000</v>
+        <v>18691000</v>
       </c>
       <c r="H61" s="3">
-        <v>17629000</v>
+        <v>18236000</v>
       </c>
       <c r="I61" s="3">
-        <v>13486000</v>
+        <v>13503000</v>
       </c>
       <c r="J61" s="3">
-        <v>12156000</v>
+        <v>12175000</v>
       </c>
       <c r="K61" s="3">
         <v>10723000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>17267000</v>
+        <v>13314000</v>
       </c>
       <c r="E62" s="3">
-        <v>8086000</v>
+        <v>4493000</v>
       </c>
       <c r="F62" s="3">
-        <v>6771000</v>
+        <v>2452000</v>
       </c>
       <c r="G62" s="3">
-        <v>8383000</v>
+        <v>2626000</v>
       </c>
       <c r="H62" s="3">
-        <v>7682000</v>
+        <v>2551000</v>
       </c>
       <c r="I62" s="3">
-        <v>5922000</v>
+        <v>2340000</v>
       </c>
       <c r="J62" s="3">
-        <v>6522000</v>
+        <v>2329000</v>
       </c>
       <c r="K62" s="3">
         <v>5621000</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>45773000</v>
+        <v>45712000</v>
       </c>
       <c r="E66" s="3">
-        <v>31733000</v>
+        <v>31685000</v>
       </c>
       <c r="F66" s="3">
-        <v>32026000</v>
+        <v>31955000</v>
       </c>
       <c r="G66" s="3">
-        <v>34477000</v>
+        <v>34413000</v>
       </c>
       <c r="H66" s="3">
-        <v>34596000</v>
+        <v>34533000</v>
       </c>
       <c r="I66" s="3">
-        <v>26704000</v>
+        <v>26652000</v>
       </c>
       <c r="J66" s="3">
-        <v>26424000</v>
+        <v>26365000</v>
       </c>
       <c r="K66" s="3">
         <v>22608000</v>
@@ -3319,7 +3319,7 @@
         <v>45821000</v>
       </c>
       <c r="G72" s="3">
-        <v>43761000</v>
+        <v>43821000</v>
       </c>
       <c r="H72" s="3">
         <v>42135000</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1987000</v>
+        <v>1505000</v>
       </c>
       <c r="E83" s="3">
-        <v>1831000</v>
+        <v>1333000</v>
       </c>
       <c r="F83" s="3">
-        <v>1915000</v>
+        <v>1386000</v>
       </c>
       <c r="G83" s="3">
-        <v>1911000</v>
+        <v>1374000</v>
       </c>
       <c r="H83" s="3">
-        <v>1593000</v>
+        <v>1252000</v>
       </c>
       <c r="I83" s="3">
-        <v>1488000</v>
+        <v>1239000</v>
       </c>
       <c r="J83" s="3">
-        <v>1544000</v>
+        <v>1099000</v>
       </c>
       <c r="K83" s="3">
         <v>1474000</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3311000</v>
+        <v>3311000</v>
       </c>
       <c r="E96" s="3">
-        <v>-3369000</v>
+        <v>3369000</v>
       </c>
       <c r="F96" s="3">
-        <v>-3420000</v>
+        <v>3420000</v>
       </c>
       <c r="G96" s="3">
-        <v>-3388000</v>
+        <v>3388000</v>
       </c>
       <c r="H96" s="3">
-        <v>-3316000</v>
+        <v>3316000</v>
       </c>
       <c r="I96" s="3">
-        <v>-3193000</v>
+        <v>3193000</v>
       </c>
       <c r="J96" s="3">
-        <v>-2803000</v>
+        <v>2803000</v>
       </c>
       <c r="K96" s="3">
         <v>-2678000</v>

--- a/AAII_Financials/Yearly/MMM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MMM_YR_FIN.xlsx
@@ -656,207 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>32681000</v>
+        <v>24575000</v>
       </c>
       <c r="E8" s="3">
-        <v>34229000</v>
+        <v>24610000</v>
       </c>
       <c r="F8" s="3">
+        <v>26161000</v>
+      </c>
+      <c r="G8" s="3">
         <v>35355000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32184000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>32136000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32765000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>31657000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30109000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30274000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>31821000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>30871000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29904000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>29611000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>18376000</v>
+        <v>14417000</v>
       </c>
       <c r="E9" s="3">
-        <v>19232000</v>
+        <v>14894000</v>
       </c>
       <c r="F9" s="3">
+        <v>15853000</v>
+      </c>
+      <c r="G9" s="3">
         <v>18795000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16499000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17064000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16655000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15969000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15115000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15341000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16437000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16087000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15685000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15693000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>14305000</v>
+        <v>10158000</v>
       </c>
       <c r="E10" s="3">
-        <v>14997000</v>
+        <v>9716000</v>
       </c>
       <c r="F10" s="3">
+        <v>10308000</v>
+      </c>
+      <c r="G10" s="3">
         <v>16560000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15685000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>15072000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>16110000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>15688000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14994000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14933000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15384000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14784000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14219000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13918000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +888,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1810000</v>
+        <v>1070000</v>
       </c>
       <c r="E12" s="3">
+        <v>1123000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1160000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1994000</v>
+      </c>
+      <c r="H12" s="3">
         <v>1862000</v>
       </c>
-      <c r="F12" s="3">
-        <v>1994000</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
+        <v>1874000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1816000</v>
+      </c>
+      <c r="K12" s="3">
         <v>1862000</v>
       </c>
-      <c r="H12" s="3">
-        <v>1874000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1816000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1862000</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1764000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1751000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1770000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1715000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1634000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1570000</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,41 +981,44 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>14883000</v>
+        <v>-1268000</v>
       </c>
       <c r="E14" s="3">
-        <v>-344000</v>
+        <v>14861000</v>
       </c>
       <c r="F14" s="3">
+        <v>-1253000</v>
+      </c>
+      <c r="G14" s="3">
         <v>88000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-139000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>330000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>487000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-487000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-111000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>114000</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>10</v>
@@ -1008,36 +1029,39 @@
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1987000</v>
+        <v>1180000</v>
       </c>
       <c r="E15" s="3">
-        <v>1831000</v>
+        <v>1429000</v>
       </c>
       <c r="F15" s="3">
+        <v>1254000</v>
+      </c>
+      <c r="G15" s="3">
         <v>1915000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1911000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1593000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1488000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1337000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1077,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>26797000</v>
+        <v>20285000</v>
       </c>
       <c r="E17" s="3">
-        <v>27786000</v>
+        <v>20329000</v>
       </c>
       <c r="F17" s="3">
+        <v>22813000</v>
+      </c>
+      <c r="G17" s="3">
         <v>27601000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25028000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25831000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24998000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24324000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23082000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23328000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24686000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24205000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23421000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23433000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>5884000</v>
+        <v>4290000</v>
       </c>
       <c r="E18" s="3">
-        <v>6443000</v>
+        <v>4281000</v>
       </c>
       <c r="F18" s="3">
+        <v>3348000</v>
+      </c>
+      <c r="G18" s="3">
         <v>7754000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7156000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6305000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7767000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7333000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7027000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6946000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7135000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6666000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6483000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6178000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-18000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-11000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-10000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-36000</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="3">
         <v>424000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>39000</v>
       </c>
       <c r="P20" s="3">
         <v>39000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>39000</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7889000</v>
+        <v>5479000</v>
       </c>
       <c r="E21" s="3">
-        <v>8285000</v>
+        <v>5728000</v>
       </c>
       <c r="F21" s="3">
+        <v>4613000</v>
+      </c>
+      <c r="G21" s="3">
         <v>9679000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9062000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7934000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9255000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8670000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8925000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8377000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8536000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8035000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7810000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7453000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>942000</v>
+        <v>1191000</v>
       </c>
       <c r="E22" s="3">
+        <v>941000</v>
+      </c>
+      <c r="F22" s="3">
         <v>462000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>488000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>529000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>448000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>350000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>322000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>398000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>119000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>102000</v>
       </c>
       <c r="N22" s="3">
         <v>102000</v>
       </c>
       <c r="O22" s="3">
+        <v>102000</v>
+      </c>
+      <c r="P22" s="3">
         <v>171000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>186000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-9670000</v>
+        <v>4828000</v>
       </c>
       <c r="E23" s="3">
-        <v>6403000</v>
+        <v>-11253000</v>
       </c>
       <c r="F23" s="3">
+        <v>4215000</v>
+      </c>
+      <c r="G23" s="3">
         <v>7214000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6790000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5643000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7000000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7548000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7053000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6823000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7026000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6562000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6351000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6031000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-2691000</v>
+        <v>804000</v>
       </c>
       <c r="E24" s="3">
-        <v>612000</v>
+        <v>-2867000</v>
       </c>
       <c r="F24" s="3">
+        <v>188000</v>
+      </c>
+      <c r="G24" s="3">
         <v>1285000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1337000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1114000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1637000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2679000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1995000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1982000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2028000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1841000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1840000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1674000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-6979000</v>
+        <v>4024000</v>
       </c>
       <c r="E26" s="3">
-        <v>5791000</v>
+        <v>-8386000</v>
       </c>
       <c r="F26" s="3">
+        <v>4027000</v>
+      </c>
+      <c r="G26" s="3">
         <v>5929000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5453000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4529000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5363000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4869000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5058000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4841000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4998000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4721000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4511000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4357000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4173000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6995000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5777000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5921000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5449000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4517000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5349000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4858000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5050000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4833000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4956000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4659000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4444000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4283000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,20 +1642,23 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>164000</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>1407000</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>1764000</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1610,8 +1672,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>10</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>10</v>
@@ -1628,9 +1690,12 @@
       <c r="P29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E32" s="3">
         <v>18000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>11000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>10000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>36000</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L32" s="3">
         <v>-424000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-39000</v>
       </c>
       <c r="P32" s="3">
         <v>-39000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4173000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6995000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5777000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5921000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5449000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4517000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5349000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4858000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5050000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4833000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4956000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4659000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4444000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4283000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4173000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6995000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5777000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5921000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5449000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4517000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5349000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4858000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5050000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4833000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4956000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4659000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4444000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4283000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,413 +2074,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5933000</v>
+        <v>5600000</v>
       </c>
       <c r="E41" s="3">
+        <v>5735000</v>
+      </c>
+      <c r="F41" s="3">
         <v>3655000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4564000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4634000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2353000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2853000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3053000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2398000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1798000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1897000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2581000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2883000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2219000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>53000</v>
+        <v>2128000</v>
       </c>
       <c r="E42" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F42" s="3">
         <v>238000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>201000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>411000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>98000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>380000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1076000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>280000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>118000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1439000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>756000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1648000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1461000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4864000</v>
+        <v>3272000</v>
       </c>
       <c r="E43" s="3">
+        <v>3710000</v>
+      </c>
+      <c r="F43" s="3">
         <v>4635000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4770000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4830000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4963000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5123000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4982000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4501000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4260000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4315000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4352000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4186000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3976000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4822000</v>
+        <v>3698000</v>
       </c>
       <c r="E44" s="3">
+        <v>3944000</v>
+      </c>
+      <c r="F44" s="3">
         <v>5372000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4985000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4239000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4134000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4366000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4034000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3385000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3518000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3706000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3864000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3837000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3416000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>222000</v>
+        <v>750000</v>
       </c>
       <c r="E45" s="3">
+        <v>2596000</v>
+      </c>
+      <c r="F45" s="3">
         <v>353000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>229000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>193000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>719000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>246000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>195000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1162000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1292000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1390000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1180000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1076000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1168000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15884000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16379000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14688000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15403000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14982000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12971000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13709000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14277000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11726000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10986000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12303000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12733000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13630000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12240000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>244000</v>
+        <v>2505000</v>
       </c>
       <c r="E47" s="3">
+        <v>210000</v>
+      </c>
+      <c r="F47" s="3">
         <v>967000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>262000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>214000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>213000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>207000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>171000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>213000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>175000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>206000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1671000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1464000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1051000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9918000</v>
+        <v>7953000</v>
       </c>
       <c r="E48" s="3">
+        <v>8347000</v>
+      </c>
+      <c r="F48" s="3">
         <v>10007000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10287000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10285000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10191000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8738000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8866000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8516000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8515000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8489000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8652000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8378000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7666000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>17153000</v>
+        <v>7491000</v>
       </c>
       <c r="E49" s="3">
+        <v>7705000</v>
+      </c>
+      <c r="F49" s="3">
         <v>17489000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18774000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19637000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19823000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12708000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13449000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11486000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11850000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8485000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9033000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9310000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8963000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1968000</v>
+        <v>1889000</v>
       </c>
       <c r="E52" s="3">
+        <v>13160000</v>
+      </c>
+      <c r="F52" s="3">
         <v>2345000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1765000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1355000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>940000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>773000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>713000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>965000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1357000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1726000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1461000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1094000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1696000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>39868000</v>
+      </c>
+      <c r="E54" s="3">
         <v>50580000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>46455000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>47072000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>47344000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44659000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36500000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>37987000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32906000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32883000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31209000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33550000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33876000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31616000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3245000</v>
+        <v>2660000</v>
       </c>
       <c r="E57" s="3">
+        <v>2776000</v>
+      </c>
+      <c r="F57" s="3">
         <v>3183000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2994000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2561000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2228000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2266000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1945000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1798000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1694000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1807000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1799000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1762000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1643000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3172000</v>
+        <v>2082000</v>
       </c>
       <c r="E58" s="3">
+        <v>3139000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2199000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1577000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1084000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3063000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1242000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1854000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>972000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2044000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>106000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1683000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1085000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>682000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6619000</v>
+        <v>4755000</v>
       </c>
       <c r="E59" s="3">
+        <v>7637000</v>
+      </c>
+      <c r="F59" s="3">
         <v>2150000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2090000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2346000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2092000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1852000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1948000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3449000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3380000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4085000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4016000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3353000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3116000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11256000</v>
+      </c>
+      <c r="E60" s="3">
         <v>15297000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9523000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9035000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7948000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9222000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7244000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7687000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6219000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7118000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5964000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7498000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6200000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5441000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>13770000</v>
+        <v>11577000</v>
       </c>
       <c r="E61" s="3">
+        <v>13612000</v>
+      </c>
+      <c r="F61" s="3">
         <v>14758000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16740000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18691000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18236000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13503000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12175000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10723000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8799000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6764000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4384000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4987000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4484000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>13314000</v>
+        <v>10652000</v>
       </c>
       <c r="E62" s="3">
+        <v>14010000</v>
+      </c>
+      <c r="F62" s="3">
         <v>4493000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2452000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2626000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2551000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2340000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2329000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5621000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5498000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5339000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3720000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4649000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5829000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35974000</v>
+      </c>
+      <c r="E66" s="3">
         <v>45712000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>31685000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31955000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34413000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34533000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26652000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26365000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>22608000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>21454000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18100000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16048000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16301000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16196000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>36797000</v>
+      </c>
+      <c r="E72" s="3">
         <v>37479000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>47950000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>45821000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>43821000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>42135000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>40636000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>39115000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>37907000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>36296000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>34317000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>32416000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>30679000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>28348000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3842000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4807000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14722000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15046000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12867000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10063000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9796000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11563000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10298000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11429000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13109000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17502000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17575000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15420000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4173000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6995000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5777000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5921000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5449000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4517000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5349000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4858000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5050000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4833000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4956000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4659000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4444000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4283000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1505000</v>
+        <v>1072000</v>
       </c>
       <c r="E83" s="3">
-        <v>1333000</v>
+        <v>1302000</v>
       </c>
       <c r="F83" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="G83" s="3">
         <v>1386000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1374000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1252000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1239000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1099000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1474000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1435000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1408000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1371000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1288000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1236000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1819000</v>
+      </c>
+      <c r="E89" s="3">
         <v>6680000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5591000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7454000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8113000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7070000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6439000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6240000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6662000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6420000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6626000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5817000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5300000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5284000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1181000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1615000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1749000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1603000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1501000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1699000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1577000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1373000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1420000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1461000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1493000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1665000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1484000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1379000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3206000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1207000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1046000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1317000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-580000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6444000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>222000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3086000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1403000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2817000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-596000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-856000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2686000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2718000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4455,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1982000</v>
+      </c>
+      <c r="E96" s="3">
         <v>3311000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3369000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3420000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3388000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3316000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3193000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2803000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2678000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2561000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2216000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1730000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1635000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1555000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1098000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3147000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5350000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6145000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5300000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1124000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6701000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2655000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4626000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3648000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6603000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5246000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2058000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3675000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-48000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-104000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-62000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>48000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-160000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>156000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-33000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-54000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-111000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-17000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>108000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-333000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2278000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-909000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-70000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2281000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-500000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>655000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>600000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-99000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-684000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-302000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>664000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1158000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MMM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MMM_YR_FIN.xlsx
@@ -991,13 +991,13 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-1268000</v>
+        <v>-1377000</v>
       </c>
       <c r="E14" s="3">
         <v>14861000</v>
       </c>
       <c r="F14" s="3">
-        <v>-1253000</v>
+        <v>-1152000</v>
       </c>
       <c r="G14" s="3">
         <v>88000</v>
@@ -1104,13 +1104,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>20285000</v>
+        <v>20394000</v>
       </c>
       <c r="E17" s="3">
         <v>20329000</v>
       </c>
       <c r="F17" s="3">
-        <v>22813000</v>
+        <v>22712000</v>
       </c>
       <c r="G17" s="3">
         <v>27601000</v>
@@ -1152,13 +1152,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4290000</v>
+        <v>4181000</v>
       </c>
       <c r="E18" s="3">
         <v>4281000</v>
       </c>
       <c r="F18" s="3">
-        <v>3348000</v>
+        <v>3449000</v>
       </c>
       <c r="G18" s="3">
         <v>7754000</v>
@@ -1268,13 +1268,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5479000</v>
+        <v>5370000</v>
       </c>
       <c r="E21" s="3">
         <v>5728000</v>
       </c>
       <c r="F21" s="3">
-        <v>4613000</v>
+        <v>4714000</v>
       </c>
       <c r="G21" s="3">
         <v>9679000</v>

--- a/AAII_Financials/Yearly/MMM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MMM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>MMM</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>24948000</v>
+      </c>
+      <c r="E8" s="3">
         <v>24575000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>24610000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26161000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>35355000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>32184000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32136000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32765000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>31657000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30109000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>30274000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>31821000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>30871000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>29904000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>29611000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>14990000</v>
+      </c>
+      <c r="E9" s="3">
         <v>14417000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>14894000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15853000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18795000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16499000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17064000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16655000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15969000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15115000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15341000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16437000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16087000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15685000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15693000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9958000</v>
+      </c>
+      <c r="E10" s="3">
         <v>10158000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9716000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10308000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>16560000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>15685000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15072000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>16110000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15688000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14994000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14933000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15384000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14784000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14219000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13918000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,56 +901,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1169000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1070000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1123000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1160000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1994000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1862000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1874000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1816000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1862000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1764000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1751000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1770000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1715000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1634000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1570000</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -984,44 +1000,47 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-219000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1377000</v>
       </c>
-      <c r="E14" s="3">
-        <v>14861000</v>
-      </c>
       <c r="F14" s="3">
+        <v>379000</v>
+      </c>
+      <c r="G14" s="3">
         <v>-1152000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>88000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-139000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>330000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>487000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-487000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-111000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>114000</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>10</v>
@@ -1032,39 +1051,42 @@
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1180000</v>
+        <v>1308000</v>
       </c>
       <c r="E15" s="3">
-        <v>1429000</v>
+        <v>1224000</v>
       </c>
       <c r="F15" s="3">
+        <v>1433000</v>
+      </c>
+      <c r="G15" s="3">
         <v>1254000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1915000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1911000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1593000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1488000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1337000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1080,9 +1102,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20240000</v>
+      </c>
+      <c r="E17" s="3">
         <v>20394000</v>
       </c>
-      <c r="E17" s="3">
-        <v>20329000</v>
-      </c>
       <c r="F17" s="3">
+        <v>34811000</v>
+      </c>
+      <c r="G17" s="3">
         <v>22712000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>27601000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25028000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25831000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24998000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24324000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23082000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23328000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24686000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24205000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23421000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23433000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4708000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4181000</v>
       </c>
-      <c r="E18" s="3">
-        <v>4281000</v>
-      </c>
       <c r="F18" s="3">
+        <v>-10201000</v>
+      </c>
+      <c r="G18" s="3">
         <v>3449000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7754000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7156000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6305000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7767000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7333000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7027000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6946000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7135000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6666000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6483000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6178000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,248 +1246,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-9000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-18000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-11000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-36000</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M20" s="3">
         <v>424000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>39000</v>
       </c>
       <c r="Q20" s="3">
         <v>39000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>39000</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5370000</v>
+        <v>6068000</v>
       </c>
       <c r="E21" s="3">
-        <v>5728000</v>
+        <v>5414000</v>
       </c>
       <c r="F21" s="3">
+        <v>-8750000</v>
+      </c>
+      <c r="G21" s="3">
         <v>4714000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9679000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9062000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7934000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9255000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8670000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8925000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8377000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8536000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8035000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7810000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7453000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>946000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1191000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>941000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>462000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>488000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>529000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>448000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>350000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>322000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>398000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>119000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>102000</v>
       </c>
       <c r="O22" s="3">
         <v>102000</v>
       </c>
       <c r="P22" s="3">
+        <v>102000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>171000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>186000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4265000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4828000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11253000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4215000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7214000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6790000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5643000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7000000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7548000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7053000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6823000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7026000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6562000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6351000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6031000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1003000</v>
+      </c>
+      <c r="E24" s="3">
         <v>804000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2867000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>188000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1285000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1337000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1114000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1637000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2679000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1995000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1982000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2028000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1841000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1840000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1674000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3262000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4024000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8386000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4027000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5929000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5453000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4529000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5363000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4869000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5058000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4841000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4998000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4721000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4511000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4357000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3250000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4173000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6995000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5777000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5921000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5449000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4517000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5349000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4858000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5050000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4833000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4956000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4659000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4444000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4283000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,24 +1702,27 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>164000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>1407000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>1764000</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
@@ -1675,8 +1735,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>10</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>10</v>
@@ -1693,9 +1753,12 @@
       <c r="Q29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E32" s="3">
         <v>9000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>18000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>11000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>36000</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M32" s="3">
         <v>-424000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-39000</v>
       </c>
       <c r="Q32" s="3">
         <v>-39000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3250000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4173000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6995000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5777000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5921000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5449000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4517000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5349000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4858000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5050000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4833000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4956000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4659000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4444000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4283000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3250000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4173000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6995000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5777000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5921000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5449000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4517000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5349000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4858000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5050000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4833000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4956000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4659000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4444000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4283000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,440 +2160,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5235000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5600000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5735000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3655000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4564000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4634000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2353000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2853000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3053000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2398000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1798000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1897000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2581000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2883000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2219000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2698000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2128000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>50000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>238000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>201000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>411000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>98000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>380000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1076000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>280000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>118000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1439000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>756000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1648000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1461000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3272000</v>
+        <v>3533000</v>
       </c>
       <c r="E43" s="3">
+        <v>3194000</v>
+      </c>
+      <c r="F43" s="3">
         <v>3710000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4635000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4770000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4830000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4963000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5123000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4982000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4501000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4260000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4315000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4352000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4186000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3976000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3661000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3698000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3944000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5372000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4985000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4239000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4134000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4366000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4034000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3385000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3518000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3706000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3864000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3837000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3416000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>750000</v>
+        <v>869000</v>
       </c>
       <c r="E45" s="3">
+        <v>771000</v>
+      </c>
+      <c r="F45" s="3">
         <v>2596000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>353000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>229000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>193000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>719000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>246000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>195000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1162000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1292000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1390000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1180000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1076000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1168000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16387000</v>
+      </c>
+      <c r="E46" s="3">
         <v>15884000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16379000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14688000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15403000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14982000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12971000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13709000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14277000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11726000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10986000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12303000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12733000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13630000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12240000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>2505000</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3">
         <v>210000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>967000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>262000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>214000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>213000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>207000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>171000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>213000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>175000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>206000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1671000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1464000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1051000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7617000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7953000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8347000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10007000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10287000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10285000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10191000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8738000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8866000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8516000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8515000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8489000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8652000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8378000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7666000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7522000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7491000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7705000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17489000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18774000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19637000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19823000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12708000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13449000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11486000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11850000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8485000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9033000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9310000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8963000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1889000</v>
+        <v>2381000</v>
       </c>
       <c r="E52" s="3">
+        <v>4394000</v>
+      </c>
+      <c r="F52" s="3">
         <v>13160000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2345000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1765000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1355000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>940000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>773000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>713000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>965000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1357000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1726000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1461000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1094000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1696000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37733000</v>
+      </c>
+      <c r="E54" s="3">
         <v>39868000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>50580000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>46455000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>47072000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>47344000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44659000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36500000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37987000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32906000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32883000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31209000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33550000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>33876000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31616000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,296 +2916,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2702000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2660000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2776000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3183000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2994000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2561000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2228000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2266000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1945000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1798000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1694000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1807000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1799000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1762000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1643000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1837000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2082000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3139000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2199000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1577000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1084000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3063000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1242000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1854000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>972000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2044000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>106000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1683000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1085000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>682000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4755000</v>
+        <v>3014000</v>
       </c>
       <c r="E59" s="3">
+        <v>3195000</v>
+      </c>
+      <c r="F59" s="3">
         <v>7637000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2150000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2090000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2346000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2092000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1852000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1948000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3449000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3380000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4085000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4016000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3353000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3116000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9595000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11256000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15297000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9523000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9035000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7948000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9222000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7244000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7687000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6219000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7118000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5964000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7498000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6200000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5441000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11577000</v>
+        <v>11295000</v>
       </c>
       <c r="E61" s="3">
+        <v>11611000</v>
+      </c>
+      <c r="F61" s="3">
         <v>13612000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14758000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16740000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18691000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18236000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13503000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12175000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10723000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8799000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6764000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4384000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4987000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4484000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10652000</v>
+        <v>10047000</v>
       </c>
       <c r="E62" s="3">
+        <v>10940000</v>
+      </c>
+      <c r="F62" s="3">
         <v>14010000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4493000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2452000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2626000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2551000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2340000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2329000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5621000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5498000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5339000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3720000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4649000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5829000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32986000</v>
+      </c>
+      <c r="E66" s="3">
         <v>35974000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45712000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31685000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31955000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34413000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34533000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26652000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26365000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22608000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21454000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18100000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16048000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16301000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16196000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>38258000</v>
+      </c>
+      <c r="E72" s="3">
         <v>36797000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>37479000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>47950000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>45821000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>43821000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>42135000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>40636000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>39115000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>37907000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>36296000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>34317000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>32416000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>30679000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>28348000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4702000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3842000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4807000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14722000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15046000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12867000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10063000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9796000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11563000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10298000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11429000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13109000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17502000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17575000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15420000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3250000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4173000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6995000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5777000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5921000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5449000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4517000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5349000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4858000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5050000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4833000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4956000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4659000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4444000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4283000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1072000</v>
+        <v>1204000</v>
       </c>
       <c r="E83" s="3">
-        <v>1302000</v>
+        <v>1116000</v>
       </c>
       <c r="F83" s="3">
+        <v>1306000</v>
+      </c>
+      <c r="G83" s="3">
         <v>1129000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1386000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1374000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1252000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1239000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1099000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1474000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1435000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1408000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1371000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1288000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1236000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2306000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1819000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6680000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5591000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7454000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8113000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7070000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6439000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6240000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6662000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6420000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6626000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5817000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5300000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5284000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-910000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1181000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1615000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1749000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1603000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1501000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1699000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1577000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1373000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1420000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1461000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1493000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1665000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1484000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1379000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1350000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3206000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1207000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1046000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1317000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-580000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6444000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>222000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3086000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1403000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2817000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-596000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-856000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2686000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2718000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,56 +4688,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1562000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1982000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3311000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3369000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3420000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3388000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3316000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3193000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2803000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2678000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2561000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2216000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1730000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1635000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1555000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,151 +4889,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4016000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1098000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3147000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5350000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6145000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5300000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1124000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6701000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2655000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4626000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3648000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6603000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5246000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2058000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3675000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-44000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-48000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-104000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-62000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>48000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-160000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>156000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-33000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-54000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-111000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-17000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>108000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-49000</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-319000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-333000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2278000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-909000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-70000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2281000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-500000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-200000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>655000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>600000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-99000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-684000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-302000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>664000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1158000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
